--- a/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,77</t>
+          <t>-0,73; 1,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,65</t>
+          <t>-0,91; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>-1,41; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,37</t>
+          <t>-3,06; 0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-2,09; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,0</t>
+          <t>-1,98; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,54</t>
+          <t>-0,18; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,42</t>
+          <t>-0,52; 0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,75</t>
+          <t>-0,72; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,01</t>
+          <t>-0,9; 2,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,0</t>
+          <t>-1,13; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,38</t>
+          <t>-3,28; 0,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,0</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,25</t>
+          <t>-0,72; 0,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,33</t>
+          <t>-0,45; 0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 199,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,79</t>
+          <t>-0,73; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,75</t>
+          <t>-0,89; 2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,34</t>
+          <t>-3,11; 0,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,22 +954,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,24</t>
+          <t>-0,72; 0,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,57</t>
+          <t>-0,18; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,4</t>
+          <t>-0,52; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,42</t>
+          <t>-100,0; 217,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0.08338961256428205</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2078421625287707</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8701535266372447</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.2309988543745433</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4629765929343218</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 1,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 2,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,21</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.7260092586454352</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.894905683315444</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.765840185247211</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.649510029262267</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.212975441098859</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,84</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3064142599065762</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2789849327579156</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-71,78%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>-1.685243509162975</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,11; 0,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.83551567495418</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +741,201 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.966307571186122</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.7177906955581254</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,48</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.114793703380939</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3666858835595721</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3370136669552471</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2699835158698289</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.645228074389317</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.893374604159912</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.948269557870404</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.477125281303982</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-43,56%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>125,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-37,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 0,25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 0,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 0,42</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 217,32</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1969377427652194</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1151616450426736</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.09707885997083063</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.4355546520901797</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.253565207262312</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3701690442146265</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7248496071098467</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.1840716722681373</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5238224242818464</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2525067940675566</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5412927218598942</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4153952163391517</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2.173165577796405</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +944,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
